--- a/TestCases/Stat_TestCase.xlsx
+++ b/TestCases/Stat_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BCCD53-4677-43A0-8362-181ED01B0A5D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7755AF03-7A9C-436F-A795-5A7360F0B825}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12792" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="STAT" sheetId="16" r:id="rId1"/>
+    <sheet name="STAT" sheetId="17" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -34,19 +34,19 @@
     <t>SpringMediCareWeb</t>
   </si>
   <si>
-    <t>Module Code：</t>
+    <t>Pass</t>
   </si>
   <si>
-    <t>Test requirement:</t>
-  </si>
-  <si>
-    <t>Pass</t>
+    <t>Fail</t>
   </si>
   <si>
     <t>Pending</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>Module Code：</t>
+  </si>
+  <si>
+    <t>Test requirement:</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -76,10 +76,10 @@
     <t>Note</t>
   </si>
   <si>
-    <t>STAT400 - Statistics Management</t>
+    <t>STAT - Statistics and Reporting</t>
   </si>
   <si>
-    <t>STAT1 - Manage Statistics</t>
+    <t>Statistics and Reporting</t>
   </si>
   <si>
     <t>1. Kiểm tra thống kê thuốc</t>
@@ -468,24 +468,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -720,7 +720,7 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.77734375" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" customWidth="1"/>
     <col min="3" max="3" width="50.33203125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="18.88671875" customWidth="1"/>
@@ -733,9 +733,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -759,9 +759,9 @@
     </row>
     <row r="2" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -787,11 +787,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -815,13 +815,13 @@
     </row>
     <row r="4" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -845,13 +845,13 @@
     </row>
     <row r="5" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -875,13 +875,13 @@
     </row>
     <row r="6" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6">
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="7" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -968,21 +968,21 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="29" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="27" t="s">
         <v>13</v>
       </c>
       <c r="H9" s="32" t="s">
@@ -1010,16 +1010,16 @@
       <c r="X9" s="3"/>
     </row>
     <row r="10" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -1038,14 +1038,14 @@
     <row r="11" spans="1:24" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="35"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="22"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="25"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1065,15 +1065,15 @@
       <c r="A12" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="22"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="25"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1102,8 +1102,8 @@
       <c r="D13" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="17" t="s">
         <v>24</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>46256</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>25</v>
@@ -1135,15 +1135,15 @@
       <c r="A14" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="22"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="25"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -1172,8 +1172,8 @@
       <c r="D15" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="17" t="s">
         <v>31</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>46256</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>32</v>
@@ -1214,8 +1214,8 @@
       <c r="D16" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
       <c r="G16" s="17" t="s">
         <v>37</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>46256</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>38</v>
@@ -1256,8 +1256,8 @@
       <c r="D17" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="17" t="s">
         <v>43</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>46256</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>44</v>
@@ -26299,17 +26299,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
@@ -26320,10 +26320,10 @@
     <mergeCell ref="D9:F10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
-    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-0F00-000001000000}"/>
-    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-0F00-000002000000}"/>
-    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-0F00-000003000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
+    <hyperlink ref="G15" r:id="rId2" xr:uid="{00000000-0004-0000-1000-000001000000}"/>
+    <hyperlink ref="G16" r:id="rId3" xr:uid="{00000000-0004-0000-1000-000002000000}"/>
+    <hyperlink ref="G17" r:id="rId4" xr:uid="{00000000-0004-0000-1000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
